--- a/data/lexemes.xlsx
+++ b/data/lexemes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56DDBF00-5B8D-164E-87E4-496589B68B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94BFBC0-F15B-AD47-9EBF-92414C187020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3740" yWindow="2500" windowWidth="25700" windowHeight="14000" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
@@ -1934,9 +1934,6 @@
     <t>Omälă</t>
   </si>
   <si>
-    <t>Q_wärceznu</t>
-  </si>
-  <si>
     <t>deficient</t>
   </si>
   <si>
@@ -2346,6 +2343,9 @@
   </si>
   <si>
     <t>tasty</t>
+  </si>
+  <si>
+    <t>R_wärceznu</t>
   </si>
 </sst>
 </file>
@@ -2791,7 +2791,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>71</v>
@@ -3025,13 +3025,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>726</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>727</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>67</v>
@@ -3119,7 +3119,7 @@
         <v>582</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -3147,7 +3147,7 @@
         <v>212</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>169</v>
@@ -3158,13 +3158,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>711</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>712</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>169</v>
@@ -3189,7 +3189,7 @@
         <v>587</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>108</v>
@@ -3203,7 +3203,7 @@
         <v>107</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>108</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
@@ -3326,7 +3326,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>15</v>
@@ -3385,7 +3385,7 @@
         <v>574</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
@@ -3424,10 +3424,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>660</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>661</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>166</v>
@@ -3456,12 +3456,12 @@
         <v>574</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>12</v>
@@ -3476,16 +3476,16 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>722</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -3584,13 +3584,13 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>654</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>655</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>47</v>
@@ -3660,13 +3660,13 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>639</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>47</v>
@@ -3804,13 +3804,13 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>669</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>670</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>47</v>
@@ -3884,7 +3884,7 @@
         <v>47</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -3921,7 +3921,7 @@
         <v>574</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
@@ -4008,7 +4008,7 @@
         <v>235</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>47</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>640</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>641</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>491</v>
@@ -4304,7 +4304,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>471</v>
@@ -4446,7 +4446,7 @@
         <v>574</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
@@ -4536,12 +4536,12 @@
         <v>574</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>561</v>
@@ -4570,7 +4570,7 @@
         <v>2</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
@@ -4590,7 +4590,7 @@
         <v>574</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
@@ -4624,7 +4624,7 @@
         <v>112</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
@@ -4939,7 +4939,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>472</v>
@@ -4981,13 +4981,13 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
         <v>666</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>667</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>59</v>
@@ -5012,7 +5012,7 @@
         <v>566</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>565</v>
@@ -5054,13 +5054,13 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>648</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>649</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>59</v>
@@ -5108,21 +5108,21 @@
         <v>59</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>651</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
@@ -5175,13 +5175,13 @@
         <v>570</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>63</v>
@@ -5311,18 +5311,18 @@
         <v>518</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>686</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>687</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>518</v>
@@ -5499,7 +5499,7 @@
         <v>25</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.2">
@@ -5518,7 +5518,7 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>526</v>
@@ -5527,7 +5527,7 @@
         <v>6</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.2">
@@ -5546,13 +5546,13 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
         <v>680</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>681</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>41</v>
@@ -5600,7 +5600,7 @@
         <v>41</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
@@ -5647,10 +5647,10 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>662</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>663</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>73</v>
@@ -5675,13 +5675,13 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>496</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>41</v>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>674</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>675</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>196</v>
@@ -5745,7 +5745,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>376</v>
@@ -5841,7 +5841,7 @@
         <v>154</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.2">
@@ -5874,10 +5874,10 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>683</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>684</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>227</v>
@@ -5888,7 +5888,7 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>496</v>
@@ -5944,13 +5944,13 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="C206" s="1" t="s">
         <v>718</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>719</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>154</v>
@@ -6000,13 +6000,13 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>154</v>
@@ -6056,13 +6056,13 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>172</v>
@@ -6084,13 +6084,13 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="B216" s="1" t="s">
+      <c r="C216" s="1" t="s">
         <v>658</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>659</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>172</v>
@@ -6376,7 +6376,7 @@
         <v>115</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
@@ -6451,10 +6451,10 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>634</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>635</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>350</v>
@@ -6493,13 +6493,13 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="B245" s="1" t="s">
+      <c r="C245" s="1" t="s">
         <v>695</v>
-      </c>
-      <c r="C245" s="1" t="s">
-        <v>696</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>35</v>
@@ -6619,13 +6619,13 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B254" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="C254" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="C254" s="1" t="s">
-        <v>677</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>35</v>
@@ -6633,13 +6633,13 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>496</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>35</v>
@@ -6647,13 +6647,13 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B256" s="1" t="s">
-        <v>647</v>
-      </c>
       <c r="C256" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>35</v>
@@ -6661,10 +6661,10 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>632</v>
-      </c>
-      <c r="B257" s="1" t="s">
-        <v>633</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>334</v>
@@ -6706,7 +6706,7 @@
         <v>546</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>371</v>
@@ -6717,13 +6717,13 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="C261" s="1" t="s">
         <v>644</v>
-      </c>
-      <c r="B261" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="C261" s="1" t="s">
-        <v>645</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>531</v>
@@ -6754,27 +6754,27 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B263" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="C263" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="C263" s="1" t="s">
+      <c r="D263" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="D263" s="1" t="s">
-        <v>691</v>
-      </c>
       <c r="G263" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>740</v>
-      </c>
-      <c r="B264" s="1" t="s">
-        <v>741</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>62</v>
@@ -6785,7 +6785,7 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>156</v>
@@ -6799,10 +6799,10 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>744</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>545</v>
@@ -6813,10 +6813,10 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>313</v>
@@ -6827,13 +6827,13 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="B268" s="1" t="s">
+      <c r="C268" s="1" t="s">
         <v>747</v>
-      </c>
-      <c r="C268" s="1" t="s">
-        <v>748</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>112</v>
@@ -6841,13 +6841,13 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C269" s="1" t="s">
         <v>749</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="C269" s="1" t="s">
-        <v>750</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>35</v>
@@ -6855,10 +6855,10 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>752</v>
-      </c>
-      <c r="B270" s="1" t="s">
-        <v>753</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>24</v>
@@ -6869,13 +6869,13 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="C271" s="1" t="s">
         <v>755</v>
-      </c>
-      <c r="C271" s="1" t="s">
-        <v>756</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>35</v>
@@ -6883,13 +6883,13 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="B272" s="1" t="s">
+      <c r="C272" s="1" t="s">
         <v>758</v>
-      </c>
-      <c r="C272" s="1" t="s">
-        <v>759</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>518</v>
@@ -6897,13 +6897,13 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B273" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="C273" s="1" t="s">
         <v>760</v>
-      </c>
-      <c r="C273" s="1" t="s">
-        <v>761</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>25</v>
@@ -6911,10 +6911,10 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>766</v>
-      </c>
-      <c r="B274" s="1" t="s">
-        <v>767</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>386</v>
@@ -6925,10 +6925,10 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B275" s="1" t="s">
         <v>768</v>
-      </c>
-      <c r="B275" s="1" t="s">
-        <v>769</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>379</v>

--- a/data/lexemes.xlsx
+++ b/data/lexemes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94BFBC0-F15B-AD47-9EBF-92414C187020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FB4D6D-C330-8847-8700-7E374A365AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3740" yWindow="2500" windowWidth="25700" windowHeight="14000" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>

--- a/data/lexemes.xlsx
+++ b/data/lexemes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FB4D6D-C330-8847-8700-7E374A365AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21F2539-F504-714E-A9F9-DE2628CB4980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3740" yWindow="2500" windowWidth="25700" windowHeight="14000" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="776">
   <si>
     <t>Shape</t>
   </si>
@@ -2346,6 +2346,24 @@
   </si>
   <si>
     <t>R_wärceznu</t>
+  </si>
+  <si>
+    <t>Q_śtwarāz</t>
+  </si>
+  <si>
+    <t>fourfold</t>
+  </si>
+  <si>
+    <t>N_śtwarā</t>
+  </si>
+  <si>
+    <t>W_putäk</t>
+  </si>
+  <si>
+    <t>discord</t>
+  </si>
+  <si>
+    <t>V_päwtk</t>
   </si>
 </sst>
 </file>
@@ -2755,7 +2773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEF76C2B-797E-2544-85E2-CF60CE11F59B}">
-  <dimension ref="A1:G275"/>
+  <dimension ref="A1:G277"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.1640625" style="1" customWidth="1"/>
@@ -5815,13 +5833,13 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>84</v>
+        <v>770</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>85</v>
+        <v>771</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>83</v>
+        <v>772</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>154</v>
@@ -5829,44 +5847,44 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>493</v>
+        <v>84</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>494</v>
+        <v>85</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>495</v>
+        <v>83</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="G198" s="1" t="s">
-        <v>737</v>
-      </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>215</v>
+        <v>493</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>217</v>
+        <v>494</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>216</v>
+        <v>495</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>154</v>
       </c>
+      <c r="G199" s="1" t="s">
+        <v>737</v>
+      </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>488</v>
+        <v>215</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>489</v>
+        <v>217</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>154</v>
@@ -5874,13 +5892,13 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>682</v>
+        <v>488</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>683</v>
+        <v>489</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>154</v>
@@ -5888,13 +5906,13 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>496</v>
+        <v>683</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>497</v>
+        <v>227</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>154</v>
@@ -5902,13 +5920,13 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>490</v>
+        <v>684</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>154</v>
@@ -5916,13 +5934,13 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>185</v>
+        <v>490</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>184</v>
+        <v>492</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>186</v>
+        <v>491</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>154</v>
@@ -5930,13 +5948,13 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
-        <v>330</v>
+        <v>185</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>332</v>
+        <v>184</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>331</v>
+        <v>186</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>154</v>
@@ -5944,13 +5962,13 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>716</v>
+        <v>330</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>717</v>
+        <v>332</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>718</v>
+        <v>331</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>154</v>
@@ -5958,13 +5976,13 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>325</v>
+        <v>716</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>326</v>
+        <v>717</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>322</v>
+        <v>718</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>154</v>
@@ -5972,13 +5990,13 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>154</v>
@@ -5986,13 +6004,13 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>49</v>
+        <v>335</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>154</v>
@@ -6000,13 +6018,13 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>698</v>
+        <v>336</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>697</v>
+        <v>49</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>696</v>
+        <v>337</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>154</v>
@@ -6014,27 +6032,27 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>583</v>
+        <v>698</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>584</v>
+        <v>697</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>585</v>
+        <v>696</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>179</v>
+        <v>583</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>178</v>
+        <v>584</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>177</v>
+        <v>585</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>172</v>
@@ -6042,13 +6060,13 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>499</v>
+        <v>179</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>487</v>
+        <v>178</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>486</v>
+        <v>177</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>172</v>
@@ -6056,13 +6074,13 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>672</v>
+        <v>499</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>671</v>
+        <v>487</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>670</v>
+        <v>486</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>172</v>
@@ -6070,13 +6088,13 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>254</v>
+        <v>672</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>255</v>
+        <v>671</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>256</v>
+        <v>670</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>172</v>
@@ -6084,13 +6102,13 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
-        <v>656</v>
+        <v>254</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>657</v>
+        <v>255</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>658</v>
+        <v>256</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>172</v>
@@ -6098,13 +6116,13 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>589</v>
+        <v>656</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>590</v>
+        <v>657</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>122</v>
+        <v>658</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>172</v>
@@ -6112,13 +6130,13 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>556</v>
+        <v>589</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>171</v>
+        <v>590</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>554</v>
+        <v>122</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>172</v>
@@ -6126,13 +6144,13 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>202</v>
+        <v>556</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>203</v>
+        <v>554</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>172</v>
@@ -6140,69 +6158,69 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
-        <v>593</v>
+        <v>202</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C220" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D220" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D221" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D221" s="4" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>70</v>
+        <v>594</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>60</v>
+        <v>335</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>6</v>
+        <v>334</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>5</v>
+        <v>172</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
-        <v>195</v>
+        <v>70</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>578</v>
+        <v>60</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>194</v>
+        <v>6</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>367</v>
+        <v>195</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>366</v>
+        <v>578</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>530</v>
+        <v>194</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>26</v>
@@ -6210,13 +6228,13 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>151</v>
+        <v>367</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>149</v>
+        <v>366</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>150</v>
+        <v>530</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>26</v>
@@ -6224,13 +6242,13 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>500</v>
+        <v>151</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>489</v>
+        <v>149</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>26</v>
@@ -6238,13 +6256,13 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>418</v>
+        <v>230</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>26</v>
@@ -6252,13 +6270,13 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>372</v>
+        <v>501</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>373</v>
+        <v>502</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>174</v>
+        <v>418</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>26</v>
@@ -6266,13 +6284,13 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>503</v>
+        <v>372</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>504</v>
+        <v>373</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>543</v>
+        <v>174</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>26</v>
@@ -6280,13 +6298,13 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>579</v>
+        <v>503</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>580</v>
+        <v>504</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>581</v>
+        <v>543</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>26</v>
@@ -6294,13 +6312,13 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>5</v>
+        <v>579</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>22</v>
+        <v>580</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>4</v>
+        <v>581</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>26</v>
@@ -6308,13 +6326,13 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>352</v>
+        <v>5</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>353</v>
+        <v>22</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>521</v>
+        <v>4</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>26</v>
@@ -6322,86 +6340,86 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>509</v>
+        <v>352</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>511</v>
+        <v>353</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
-        <v>120</v>
+        <v>509</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>121</v>
+        <v>511</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>119</v>
+        <v>510</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>26</v>
+        <v>115</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>362</v>
+        <v>121</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>361</v>
+        <v>119</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
-        <v>248</v>
+        <v>360</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>249</v>
+        <v>362</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>250</v>
+        <v>361</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G236" s="1" t="s">
-        <v>737</v>
-      </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>506</v>
+        <v>248</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>489</v>
+        <v>249</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="G237" s="1" t="s">
+        <v>737</v>
+      </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>290</v>
+        <v>506</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>291</v>
+        <v>489</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>56</v>
+        <v>230</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>115</v>
@@ -6409,13 +6427,13 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>505</v>
+        <v>291</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>274</v>
+        <v>56</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>115</v>
@@ -6423,13 +6441,13 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>507</v>
+        <v>277</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>115</v>
@@ -6437,13 +6455,13 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
-        <v>114</v>
+        <v>507</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>117</v>
+        <v>508</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>116</v>
+        <v>267</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>115</v>
@@ -6451,13 +6469,13 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
-        <v>633</v>
+        <v>114</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>634</v>
+        <v>117</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>350</v>
+        <v>116</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>115</v>
@@ -6465,13 +6483,13 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
-        <v>344</v>
+        <v>633</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>345</v>
+        <v>634</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>115</v>
@@ -6479,13 +6497,13 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
-        <v>533</v>
+        <v>344</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>508</v>
+        <v>345</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>115</v>
@@ -6493,27 +6511,27 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
-        <v>693</v>
+        <v>533</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>694</v>
+        <v>508</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>695</v>
+        <v>266</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>131</v>
+        <v>693</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>130</v>
+        <v>694</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>129</v>
+        <v>695</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>35</v>
@@ -6521,13 +6539,13 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>35</v>
@@ -6535,13 +6553,13 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>483</v>
+        <v>123</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>35</v>
@@ -6549,13 +6567,13 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
-        <v>512</v>
+        <v>483</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>513</v>
+        <v>165</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>514</v>
+        <v>135</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>35</v>
@@ -6563,13 +6581,13 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
-        <v>484</v>
+        <v>512</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>391</v>
+        <v>513</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>28</v>
+        <v>514</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>35</v>
@@ -6577,13 +6595,13 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>516</v>
+        <v>391</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>517</v>
+        <v>28</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>35</v>
@@ -6591,13 +6609,13 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
-        <v>163</v>
+        <v>515</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>164</v>
+        <v>516</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>166</v>
+        <v>517</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>35</v>
@@ -6605,13 +6623,13 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
-        <v>33</v>
+        <v>163</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>34</v>
+        <v>164</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>522</v>
+        <v>166</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>35</v>
@@ -6619,13 +6637,13 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
-        <v>677</v>
+        <v>33</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>675</v>
+        <v>34</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>676</v>
+        <v>522</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>35</v>
@@ -6633,13 +6651,13 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>641</v>
+        <v>677</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>496</v>
+        <v>675</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>642</v>
+        <v>676</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>35</v>
@@ -6647,13 +6665,13 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>646</v>
+        <v>496</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>35</v>
@@ -6661,13 +6679,13 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
-        <v>769</v>
+        <v>645</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>632</v>
+        <v>646</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>334</v>
+        <v>644</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>35</v>
@@ -6675,27 +6693,27 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
-        <v>536</v>
+        <v>769</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>537</v>
+        <v>632</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>538</v>
+        <v>334</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>531</v>
+        <v>35</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>531</v>
@@ -6703,13 +6721,13 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>735</v>
+        <v>540</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>371</v>
+        <v>541</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>531</v>
@@ -6717,13 +6735,13 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
-        <v>643</v>
+        <v>546</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>644</v>
+        <v>371</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>531</v>
@@ -6731,95 +6749,95 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
-        <v>524</v>
+        <v>643</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>525</v>
+        <v>736</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>318</v>
+        <v>644</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E262" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F262" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G262" s="1" t="s">
-        <v>599</v>
+        <v>531</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
-        <v>691</v>
+        <v>524</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>688</v>
+        <v>525</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>689</v>
+        <v>318</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>690</v>
+        <v>241</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F263" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>705</v>
+        <v>599</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
-        <v>739</v>
+        <v>691</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>740</v>
+        <v>688</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>62</v>
+        <v>689</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>518</v>
+        <v>690</v>
+      </c>
+      <c r="G264" s="1" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>156</v>
+        <v>740</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>544</v>
+        <v>62</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>187</v>
+        <v>518</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>743</v>
+        <v>156</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>26</v>
+        <v>187</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>743</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>313</v>
+        <v>545</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>26</v>
@@ -6827,119 +6845,147 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>747</v>
+        <v>313</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>112</v>
+        <v>26</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>35</v>
+        <v>112</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>24</v>
+        <v>749</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>518</v>
+        <v>35</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>755</v>
+        <v>24</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>35</v>
+        <v>518</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>518</v>
+        <v>35</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>25</v>
+        <v>518</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>386</v>
+        <v>760</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A276" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="B275" s="1" t="s">
+      <c r="B276" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="C275" s="1" t="s">
+      <c r="C276" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="D275" s="1" t="s">
+      <c r="D276" s="1" t="s">
         <v>154</v>
       </c>
     </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A277" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G263">
-    <sortCondition ref="D237:D263"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G264">
+    <sortCondition ref="D238:D264"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/lexemes.xlsx
+++ b/data/lexemes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21F2539-F504-714E-A9F9-DE2628CB4980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52241006-1ED5-8A43-97EA-C781F48F39C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3740" yWindow="2500" windowWidth="25700" windowHeight="14000" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
+    <workbookView xWindow="6340" yWindow="580" windowWidth="25700" windowHeight="14000" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Affixation" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="777">
   <si>
     <t>Shape</t>
   </si>
@@ -2364,6 +2364,9 @@
   </si>
   <si>
     <t>V_päwtk</t>
+  </si>
+  <si>
+    <t>I_oklop</t>
   </si>
 </sst>
 </file>
@@ -2773,7 +2776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEF76C2B-797E-2544-85E2-CF60CE11F59B}">
-  <dimension ref="A1:G277"/>
+  <dimension ref="A1:G278"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.1640625" style="1" customWidth="1"/>
@@ -5362,6 +5365,9 @@
       <c r="D163" s="1" t="s">
         <v>518</v>
       </c>
+      <c r="G163" s="1" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
@@ -5390,6 +5396,9 @@
       <c r="D165" s="1" t="s">
         <v>518</v>
       </c>
+      <c r="G165" s="1" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
@@ -5404,6 +5413,9 @@
       <c r="D166" s="1" t="s">
         <v>518</v>
       </c>
+      <c r="G166" s="1" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
@@ -6898,6 +6910,9 @@
       <c r="D271" s="1" t="s">
         <v>518</v>
       </c>
+      <c r="G271" s="1" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
@@ -6981,6 +6996,20 @@
       </c>
       <c r="D277" s="1" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A278" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>518</v>
       </c>
     </row>
   </sheetData>

--- a/data/lexemes.xlsx
+++ b/data/lexemes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52241006-1ED5-8A43-97EA-C781F48F39C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C32340-5017-7C44-B92C-DE04FB5C0F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6340" yWindow="580" windowWidth="25700" windowHeight="14000" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="777">
   <si>
     <t>Shape</t>
   </si>
@@ -848,9 +848,6 @@
     <t>W_yokzi</t>
   </si>
   <si>
-    <t>I_ykonā</t>
-  </si>
-  <si>
     <t>at day</t>
   </si>
   <si>
@@ -884,9 +881,6 @@
     <t>W_yme</t>
   </si>
   <si>
-    <t>I_ylaṅkaṃ</t>
-  </si>
-  <si>
     <t>hanging in the air</t>
   </si>
   <si>
@@ -1595,9 +1589,6 @@
     <t>PREF</t>
   </si>
   <si>
-    <t>I_opärkā</t>
-  </si>
-  <si>
     <t>I_ṣäñäy</t>
   </si>
   <si>
@@ -2291,9 +2282,6 @@
     <t>covered in clay</t>
   </si>
   <si>
-    <t>I_atäṅkac</t>
-  </si>
-  <si>
     <t>to a hold</t>
   </si>
   <si>
@@ -2367,6 +2355,18 @@
   </si>
   <si>
     <t>I_oklop</t>
+  </si>
+  <si>
+    <t>I_ykon</t>
+  </si>
+  <si>
+    <t>I_opärk</t>
+  </si>
+  <si>
+    <t>I_ylaṅk</t>
+  </si>
+  <si>
+    <t>I_atäṅk</t>
   </si>
 </sst>
 </file>
@@ -2804,21 +2804,21 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>71</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D2" s="3">
         <v>3</v>
@@ -2840,30 +2840,30 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>67</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>67</v>
@@ -2874,13 +2874,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>67</v>
@@ -2891,10 +2891,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>139</v>
@@ -2903,15 +2903,15 @@
         <v>67</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>223</v>
@@ -2922,13 +2922,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>67</v>
@@ -2936,13 +2936,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>67</v>
@@ -2953,30 +2953,30 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>67</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>67</v>
@@ -2987,13 +2987,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>67</v>
@@ -3013,7 +3013,7 @@
         <v>67</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -3046,30 +3046,30 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>67</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>67</v>
@@ -3080,13 +3080,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>67</v>
@@ -3094,30 +3094,30 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="C20" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>67</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>67</v>
@@ -3128,33 +3128,33 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>3</v>
@@ -3168,24 +3168,24 @@
         <v>212</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>169</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>169</v>
@@ -3193,13 +3193,13 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>169</v>
@@ -3207,16 +3207,16 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -3224,7 +3224,7 @@
         <v>107</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>108</v>
@@ -3235,19 +3235,19 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>188</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -3258,10 +3258,10 @@
         <v>58</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>59</v>
@@ -3275,7 +3275,7 @@
         <v>95</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>37</v>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>174</v>
@@ -3297,18 +3297,18 @@
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="1" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>37</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>75</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>15</v>
@@ -3361,13 +3361,13 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>82</v>
@@ -3391,33 +3391,33 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>82</v>
@@ -3431,24 +3431,24 @@
         <v>168</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>166</v>
@@ -3457,32 +3457,32 @@
         <v>82</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>12</v>
@@ -3497,16 +3497,16 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>719</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -3523,18 +3523,18 @@
         <v>47</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>47</v>
@@ -3556,30 +3556,30 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C50" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>47</v>
@@ -3588,13 +3588,13 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>452</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>47</v>
@@ -3605,13 +3605,13 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>47</v>
@@ -3659,7 +3659,7 @@
         <v>47</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
@@ -3676,18 +3676,18 @@
         <v>47</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>47</v>
@@ -3707,12 +3707,12 @@
         <v>47</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>170</v>
@@ -3724,15 +3724,15 @@
         <v>47</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>150</v>
@@ -3755,21 +3755,21 @@
         <v>47</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>47</v>
@@ -3777,30 +3777,30 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="C64" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>47</v>
@@ -3820,18 +3820,18 @@
         <v>47</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>47</v>
@@ -3854,7 +3854,7 @@
         <v>47</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -3871,7 +3871,7 @@
         <v>47</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -3888,7 +3888,7 @@
         <v>47</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -3905,7 +3905,7 @@
         <v>47</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -3922,7 +3922,7 @@
         <v>47</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
@@ -3939,10 +3939,10 @@
         <v>47</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
@@ -3973,18 +3973,18 @@
         <v>47</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="C75" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>47</v>
@@ -3992,13 +3992,13 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>47</v>
@@ -4018,7 +4018,7 @@
         <v>47</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
@@ -4029,13 +4029,13 @@
         <v>235</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
@@ -4066,18 +4066,18 @@
         <v>47</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>47</v>
@@ -4088,13 +4088,13 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>47</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>74</v>
@@ -4114,35 +4114,35 @@
         <v>47</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C84" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="C85" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>47</v>
@@ -4150,13 +4150,13 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>47</v>
@@ -4164,30 +4164,30 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>47</v>
@@ -4195,30 +4195,30 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>47</v>
@@ -4238,18 +4238,18 @@
         <v>47</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>180</v>
@@ -4260,13 +4260,13 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>438</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>47</v>
@@ -4274,13 +4274,13 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>47</v>
@@ -4289,35 +4289,35 @@
         <v>2</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>47</v>
@@ -4325,30 +4325,30 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>47</v>
@@ -4356,30 +4356,30 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>265</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>47</v>
@@ -4402,7 +4402,7 @@
         <v>47</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
@@ -4424,13 +4424,13 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>47</v>
@@ -4438,13 +4438,13 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>47</v>
@@ -4452,22 +4452,22 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="C105" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
@@ -4500,13 +4500,13 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>126</v>
@@ -4514,13 +4514,13 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>161</v>
@@ -4528,13 +4528,13 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>161</v>
@@ -4554,21 +4554,21 @@
         <v>161</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>161</v>
@@ -4576,13 +4576,13 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>274</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>161</v>
@@ -4591,44 +4591,44 @@
         <v>2</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>457</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>161</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>615</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>618</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>112</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
@@ -4645,7 +4645,7 @@
         <v>112</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
@@ -4664,13 +4664,13 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>112</v>
@@ -4681,13 +4681,13 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>112</v>
@@ -4698,13 +4698,13 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>112</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>93</v>
@@ -4726,13 +4726,13 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>112</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>113</v>
@@ -4766,24 +4766,24 @@
         <v>112</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
@@ -4805,13 +4805,13 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>112</v>
@@ -4834,18 +4834,18 @@
         <v>3</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>465</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>112</v>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>228</v>
@@ -4865,7 +4865,7 @@
         <v>112</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
@@ -4912,47 +4912,47 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>112</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="C135" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>112</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D136" s="5" t="s">
         <v>112</v>
@@ -4960,13 +4960,13 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>112</v>
@@ -4974,13 +4974,13 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>112</v>
@@ -4988,13 +4988,13 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>112</v>
@@ -5002,13 +5002,13 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>59</v>
@@ -5016,13 +5016,13 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>59</v>
@@ -5030,13 +5030,13 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>59</v>
@@ -5044,30 +5044,30 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>59</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>59</v>
@@ -5075,13 +5075,13 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>59</v>
@@ -5089,13 +5089,13 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>59</v>
@@ -5103,13 +5103,13 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>59</v>
@@ -5129,26 +5129,26 @@
         <v>59</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C149" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>648</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>175</v>
@@ -5160,18 +5160,18 @@
         <v>187</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="C151" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>187</v>
@@ -5193,16 +5193,16 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>63</v>
@@ -5210,13 +5210,13 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>132</v>
@@ -5224,13 +5224,13 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>132</v>
@@ -5238,7 +5238,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>265</v>
@@ -5250,18 +5250,18 @@
         <v>132</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>132</v>
@@ -5289,13 +5289,13 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>132</v>
@@ -5315,58 +5315,55 @@
         <v>51</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="C161" s="1" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>271</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>142</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="G163" s="1" t="s">
-        <v>705</v>
+        <v>516</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
@@ -5380,12 +5377,12 @@
         <v>93</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>519</v>
+        <v>774</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>90</v>
@@ -5394,52 +5391,52 @@
         <v>89</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C166" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="D166" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C168" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>25</v>
@@ -5461,10 +5458,10 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>139</v>
@@ -5475,13 +5472,13 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C171" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>25</v>
@@ -5529,7 +5526,7 @@
         <v>25</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.2">
@@ -5548,27 +5545,27 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>41</v>
@@ -5576,13 +5573,13 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>41</v>
@@ -5590,13 +5587,13 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>487</v>
-      </c>
       <c r="C179" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>41</v>
@@ -5618,19 +5615,19 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>41</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
@@ -5677,10 +5674,10 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>73</v>
@@ -5691,13 +5688,13 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="C186" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>41</v>
@@ -5705,13 +5702,13 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>41</v>
@@ -5725,7 +5722,7 @@
         <v>156</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>41</v>
@@ -5733,10 +5730,10 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>196</v>
@@ -5775,13 +5772,13 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>41</v>
@@ -5789,13 +5786,13 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>41</v>
@@ -5803,13 +5800,13 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>41</v>
@@ -5845,13 +5842,13 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>154</v>
@@ -5873,19 +5870,19 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C199" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>495</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>154</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.2">
@@ -5904,10 +5901,10 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>230</v>
@@ -5918,10 +5915,10 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>227</v>
@@ -5932,13 +5929,13 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>154</v>
@@ -5946,13 +5943,13 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="C204" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>154</v>
@@ -5974,13 +5971,13 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="C206" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>154</v>
@@ -5988,13 +5985,13 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>154</v>
@@ -6002,13 +5999,13 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>154</v>
@@ -6016,13 +6013,13 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="C209" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>154</v>
@@ -6030,13 +6027,13 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>154</v>
@@ -6044,13 +6041,13 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>154</v>
@@ -6058,13 +6055,13 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>172</v>
@@ -6086,13 +6083,13 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>172</v>
@@ -6100,13 +6097,13 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>172</v>
@@ -6128,13 +6125,13 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>172</v>
@@ -6142,10 +6139,10 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>122</v>
@@ -6156,13 +6153,13 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>171</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>172</v>
@@ -6184,7 +6181,7 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>255</v>
@@ -6198,13 +6195,13 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>172</v>
@@ -6229,7 +6226,7 @@
         <v>195</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>194</v>
@@ -6240,13 +6237,13 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>26</v>
@@ -6268,10 +6265,10 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>230</v>
@@ -6282,13 +6279,13 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>26</v>
@@ -6296,10 +6293,10 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>174</v>
@@ -6310,13 +6307,13 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>26</v>
@@ -6324,13 +6321,13 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>26</v>
@@ -6352,13 +6349,13 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>26</v>
@@ -6366,13 +6363,13 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="C234" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>115</v>
@@ -6394,13 +6391,13 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="C236" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>115</v>
@@ -6420,15 +6417,15 @@
         <v>115</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>230</v>
@@ -6439,10 +6436,10 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>56</v>
@@ -6453,13 +6450,13 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>115</v>
@@ -6467,10 +6464,10 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>267</v>
@@ -6495,13 +6492,13 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>115</v>
@@ -6509,13 +6506,13 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>115</v>
@@ -6523,10 +6520,10 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>266</v>
@@ -6537,13 +6534,13 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>35</v>
@@ -6579,7 +6576,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>165</v>
@@ -6593,13 +6590,13 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C250" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C250" s="1" t="s">
-        <v>514</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>35</v>
@@ -6607,10 +6604,10 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>28</v>
@@ -6621,13 +6618,13 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C252" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C252" s="1" t="s">
-        <v>517</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>35</v>
@@ -6655,7 +6652,7 @@
         <v>34</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>35</v>
@@ -6663,13 +6660,13 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>35</v>
@@ -6677,13 +6674,13 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>35</v>
@@ -6691,13 +6688,13 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>35</v>
@@ -6705,13 +6702,13 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>35</v>
@@ -6719,69 +6716,69 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>241</v>
@@ -6793,49 +6790,49 @@
         <v>3</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>187</v>
@@ -6843,13 +6840,13 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>26</v>
@@ -6857,13 +6854,13 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>26</v>
@@ -6871,13 +6868,13 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>112</v>
@@ -6885,13 +6882,13 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>35</v>
@@ -6899,30 +6896,30 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
-        <v>751</v>
+        <v>776</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>35</v>
@@ -6930,27 +6927,27 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>25</v>
@@ -6958,13 +6955,13 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>47</v>
@@ -6972,13 +6969,13 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>154</v>
@@ -6986,13 +6983,13 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>47</v>
@@ -7000,16 +6997,16 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>

--- a/data/lexemes.xlsx
+++ b/data/lexemes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C32340-5017-7C44-B92C-DE04FB5C0F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A833F842-3391-3340-A180-4FA4D849C18F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6340" yWindow="580" windowWidth="25700" windowHeight="14000" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
+    <workbookView xWindow="4220" yWindow="580" windowWidth="25700" windowHeight="14000" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Affixation" sheetId="3" r:id="rId1"/>
@@ -923,9 +923,6 @@
     <t>V_räk</t>
   </si>
   <si>
-    <t>S_lānt</t>
-  </si>
-  <si>
     <t>shining</t>
   </si>
   <si>
@@ -2367,6 +2364,9 @@
   </si>
   <si>
     <t>I_atäṅk</t>
+  </si>
+  <si>
+    <t>W_wlāñ</t>
   </si>
 </sst>
 </file>
@@ -2804,21 +2804,21 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>71</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D2" s="3">
         <v>3</v>
@@ -2840,30 +2840,30 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>67</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>67</v>
@@ -2874,13 +2874,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>67</v>
@@ -2891,10 +2891,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>139</v>
@@ -2903,15 +2903,15 @@
         <v>67</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>223</v>
@@ -2936,13 +2936,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>67</v>
@@ -2953,30 +2953,30 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>67</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>67</v>
@@ -2987,13 +2987,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>67</v>
@@ -3013,7 +3013,7 @@
         <v>67</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -3046,30 +3046,30 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>722</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>723</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>67</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>623</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>624</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>67</v>
@@ -3080,13 +3080,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>67</v>
@@ -3094,30 +3094,30 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>67</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>621</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>67</v>
@@ -3128,33 +3128,33 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>3</v>
@@ -3168,24 +3168,24 @@
         <v>212</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>169</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>707</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>708</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>169</v>
@@ -3193,13 +3193,13 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>295</v>
+        <v>776</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>169</v>
@@ -3207,16 +3207,16 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -3224,7 +3224,7 @@
         <v>107</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>108</v>
@@ -3235,19 +3235,19 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>188</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -3258,10 +3258,10 @@
         <v>58</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>59</v>
@@ -3275,7 +3275,7 @@
         <v>95</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>37</v>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>174</v>
@@ -3297,18 +3297,18 @@
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>304</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>37</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>408</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>75</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>15</v>
@@ -3364,7 +3364,7 @@
         <v>293</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>294</v>
@@ -3391,33 +3391,33 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>357</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>611</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>82</v>
@@ -3431,24 +3431,24 @@
         <v>168</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>656</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>657</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>166</v>
@@ -3457,32 +3457,32 @@
         <v>82</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>12</v>
@@ -3497,16 +3497,16 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>718</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -3523,18 +3523,18 @@
         <v>47</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>447</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>47</v>
@@ -3556,30 +3556,30 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="C49" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>47</v>
@@ -3588,13 +3588,13 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>450</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>47</v>
@@ -3605,13 +3605,13 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>650</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>651</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>47</v>
@@ -3659,7 +3659,7 @@
         <v>47</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
@@ -3676,18 +3676,18 @@
         <v>47</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>634</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>635</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>47</v>
@@ -3707,12 +3707,12 @@
         <v>47</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>170</v>
@@ -3724,15 +3724,15 @@
         <v>47</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>150</v>
@@ -3755,21 +3755,21 @@
         <v>47</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="C62" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>47</v>
@@ -3777,30 +3777,30 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>443</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>47</v>
@@ -3820,18 +3820,18 @@
         <v>47</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>665</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>666</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>47</v>
@@ -3854,7 +3854,7 @@
         <v>47</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -3871,7 +3871,7 @@
         <v>47</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -3888,7 +3888,7 @@
         <v>47</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -3905,7 +3905,7 @@
         <v>47</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -3922,7 +3922,7 @@
         <v>47</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
@@ -3939,10 +3939,10 @@
         <v>47</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
@@ -3973,18 +3973,18 @@
         <v>47</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>47</v>
@@ -3992,13 +3992,13 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="C76" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>47</v>
@@ -4018,7 +4018,7 @@
         <v>47</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
@@ -4029,13 +4029,13 @@
         <v>235</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
@@ -4066,7 +4066,7 @@
         <v>47</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
@@ -4088,13 +4088,13 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="C82" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>47</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>74</v>
@@ -4114,7 +4114,7 @@
         <v>47</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
@@ -4131,18 +4131,18 @@
         <v>47</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>438</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>47</v>
@@ -4150,13 +4150,13 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>47</v>
@@ -4164,30 +4164,30 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>47</v>
@@ -4195,30 +4195,30 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>47</v>
@@ -4238,18 +4238,18 @@
         <v>47</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>180</v>
@@ -4260,13 +4260,13 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>47</v>
@@ -4274,13 +4274,13 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>47</v>
@@ -4289,35 +4289,35 @@
         <v>2</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="C95" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="C96" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>47</v>
@@ -4325,30 +4325,30 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="C98" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>47</v>
@@ -4356,19 +4356,19 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>265</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
@@ -4402,7 +4402,7 @@
         <v>47</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
@@ -4424,13 +4424,13 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>47</v>
@@ -4438,13 +4438,13 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="C104" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>47</v>
@@ -4452,22 +4452,22 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
@@ -4500,13 +4500,13 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>608</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>126</v>
@@ -4514,13 +4514,13 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>161</v>
@@ -4528,13 +4528,13 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>161</v>
@@ -4554,21 +4554,21 @@
         <v>161</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>161</v>
@@ -4591,44 +4591,44 @@
         <v>2</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="C114" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>455</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>161</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>613</v>
-      </c>
       <c r="C115" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>112</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
@@ -4645,7 +4645,7 @@
         <v>112</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
@@ -4664,13 +4664,13 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>112</v>
@@ -4681,13 +4681,13 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>112</v>
@@ -4698,13 +4698,13 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>475</v>
-      </c>
       <c r="C120" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>112</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>93</v>
@@ -4726,13 +4726,13 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>547</v>
-      </c>
       <c r="C122" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>112</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>113</v>
@@ -4766,24 +4766,24 @@
         <v>112</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
@@ -4805,13 +4805,13 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>112</v>
@@ -4834,18 +4834,18 @@
         <v>3</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>463</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>112</v>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>228</v>
@@ -4865,7 +4865,7 @@
         <v>112</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
@@ -4912,47 +4912,47 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>112</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>112</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B136" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>457</v>
       </c>
       <c r="D136" s="5" t="s">
         <v>112</v>
@@ -4960,13 +4960,13 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>471</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>112</v>
@@ -4974,13 +4974,13 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>469</v>
-      </c>
       <c r="C138" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>112</v>
@@ -4988,13 +4988,13 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>618</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>112</v>
@@ -5002,13 +5002,13 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
         <v>662</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>663</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>59</v>
@@ -5016,13 +5016,13 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="C141" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>566</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>59</v>
@@ -5030,13 +5030,13 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>59</v>
@@ -5044,30 +5044,30 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>59</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="C144" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>594</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>59</v>
@@ -5075,13 +5075,13 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>644</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>645</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>59</v>
@@ -5089,13 +5089,13 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>59</v>
@@ -5103,13 +5103,13 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>59</v>
@@ -5129,26 +5129,26 @@
         <v>59</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>647</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>175</v>
@@ -5160,18 +5160,18 @@
         <v>187</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C151" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>318</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>187</v>
@@ -5193,16 +5193,16 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>63</v>
@@ -5210,13 +5210,13 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="C154" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>132</v>
@@ -5224,13 +5224,13 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>132</v>
@@ -5238,7 +5238,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>265</v>
@@ -5250,18 +5250,18 @@
         <v>132</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>413</v>
-      </c>
       <c r="C157" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>132</v>
@@ -5289,13 +5289,13 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>132</v>
@@ -5315,7 +5315,7 @@
         <v>51</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
@@ -5326,35 +5326,35 @@
         <v>275</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>683</v>
-      </c>
       <c r="D162" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>270</v>
@@ -5363,7 +5363,7 @@
         <v>142</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
@@ -5377,12 +5377,12 @@
         <v>93</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>90</v>
@@ -5391,15 +5391,15 @@
         <v>89</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>281</v>
@@ -5408,35 +5408,35 @@
         <v>282</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="C168" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>25</v>
@@ -5458,10 +5458,10 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>139</v>
@@ -5472,13 +5472,13 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="C171" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>398</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>25</v>
@@ -5526,7 +5526,7 @@
         <v>25</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.2">
@@ -5545,27 +5545,27 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="C177" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>41</v>
@@ -5573,13 +5573,13 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>677</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>41</v>
@@ -5587,13 +5587,13 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C179" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>484</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>41</v>
@@ -5615,19 +5615,19 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>41</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
@@ -5674,10 +5674,10 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>658</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>659</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>73</v>
@@ -5702,13 +5702,13 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C187" s="1" t="s">
         <v>697</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>698</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>41</v>
@@ -5722,7 +5722,7 @@
         <v>156</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>41</v>
@@ -5730,10 +5730,10 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>670</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>671</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>196</v>
@@ -5772,13 +5772,13 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>41</v>
@@ -5786,13 +5786,13 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>41</v>
@@ -5800,13 +5800,13 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="C194" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>41</v>
@@ -5842,13 +5842,13 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="C197" s="1" t="s">
         <v>767</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>768</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>154</v>
@@ -5870,19 +5870,19 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="C199" s="1" t="s">
         <v>492</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>493</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>154</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.2">
@@ -5901,10 +5901,10 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>230</v>
@@ -5915,10 +5915,10 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>679</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>680</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>227</v>
@@ -5929,13 +5929,13 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B203" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C203" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>495</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>154</v>
@@ -5943,13 +5943,13 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C204" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>154</v>
@@ -5971,13 +5971,13 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C206" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>154</v>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="B207" s="1" t="s">
+      <c r="C207" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>715</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>154</v>
@@ -5999,13 +5999,13 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C208" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>154</v>
@@ -6013,13 +6013,13 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C209" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>154</v>
@@ -6027,13 +6027,13 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>154</v>
@@ -6041,13 +6041,13 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>154</v>
@@ -6055,13 +6055,13 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="C212" s="1" t="s">
         <v>581</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>582</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>172</v>
@@ -6083,13 +6083,13 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>172</v>
@@ -6097,13 +6097,13 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>172</v>
@@ -6125,13 +6125,13 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="B217" s="1" t="s">
+      <c r="C217" s="1" t="s">
         <v>654</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>655</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>172</v>
@@ -6139,10 +6139,10 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>586</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>587</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>122</v>
@@ -6153,13 +6153,13 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>171</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>172</v>
@@ -6181,7 +6181,7 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>255</v>
@@ -6195,13 +6195,13 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>172</v>
@@ -6226,7 +6226,7 @@
         <v>195</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>194</v>
@@ -6237,13 +6237,13 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>26</v>
@@ -6265,10 +6265,10 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>230</v>
@@ -6279,13 +6279,13 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="C228" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>26</v>
@@ -6293,10 +6293,10 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>174</v>
@@ -6307,13 +6307,13 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="C230" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>26</v>
@@ -6321,13 +6321,13 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="B231" s="1" t="s">
+      <c r="C231" s="1" t="s">
         <v>577</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>578</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>26</v>
@@ -6349,13 +6349,13 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="C233" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>26</v>
@@ -6363,13 +6363,13 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C234" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>508</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>115</v>
@@ -6391,13 +6391,13 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C236" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>115</v>
@@ -6417,15 +6417,15 @@
         <v>115</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>230</v>
@@ -6453,7 +6453,7 @@
         <v>276</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>273</v>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="B241" s="1" t="s">
-        <v>506</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>267</v>
@@ -6492,13 +6492,13 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="B243" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="C243" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>115</v>
@@ -6506,13 +6506,13 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B244" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="C244" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>115</v>
@@ -6520,10 +6520,10 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>266</v>
@@ -6534,13 +6534,13 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="B246" s="1" t="s">
+      <c r="C246" s="1" t="s">
         <v>691</v>
-      </c>
-      <c r="C246" s="1" t="s">
-        <v>692</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>35</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>165</v>
@@ -6590,13 +6590,13 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B250" s="1" t="s">
+      <c r="C250" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="C250" s="1" t="s">
-        <v>512</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>35</v>
@@ -6604,10 +6604,10 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>28</v>
@@ -6618,13 +6618,13 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B252" s="1" t="s">
+      <c r="C252" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="C252" s="1" t="s">
-        <v>515</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>35</v>
@@ -6652,7 +6652,7 @@
         <v>34</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>35</v>
@@ -6660,13 +6660,13 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B255" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="C255" s="1" t="s">
         <v>672</v>
-      </c>
-      <c r="C255" s="1" t="s">
-        <v>673</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>35</v>
@@ -6674,13 +6674,13 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C256" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>639</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>35</v>
@@ -6688,13 +6688,13 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="B257" s="1" t="s">
-        <v>643</v>
-      </c>
       <c r="C257" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>35</v>
@@ -6702,13 +6702,13 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>35</v>
@@ -6716,69 +6716,69 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B259" s="1" t="s">
+      <c r="C259" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="C259" s="1" t="s">
-        <v>535</v>
-      </c>
       <c r="D259" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="B260" s="1" t="s">
+      <c r="C260" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C260" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="D260" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="C262" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>733</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>641</v>
-      </c>
       <c r="D262" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>522</v>
-      </c>
       <c r="C263" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>241</v>
@@ -6790,49 +6790,49 @@
         <v>3</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B264" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="C264" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="C264" s="1" t="s">
+      <c r="D264" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="D264" s="1" t="s">
-        <v>687</v>
-      </c>
       <c r="G264" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="B265" s="1" t="s">
         <v>736</v>
-      </c>
-      <c r="B265" s="1" t="s">
-        <v>737</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>187</v>
@@ -6840,13 +6840,13 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B267" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="B267" s="1" t="s">
-        <v>740</v>
-      </c>
       <c r="C267" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>26</v>
@@ -6854,13 +6854,13 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>26</v>
@@ -6868,13 +6868,13 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="B269" s="1" t="s">
+      <c r="C269" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="C269" s="1" t="s">
-        <v>744</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>112</v>
@@ -6882,13 +6882,13 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="C270" s="1" t="s">
         <v>745</v>
-      </c>
-      <c r="B270" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="C270" s="1" t="s">
-        <v>746</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>35</v>
@@ -6896,30 +6896,30 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="B272" s="1" t="s">
+      <c r="C272" s="1" t="s">
         <v>750</v>
-      </c>
-      <c r="C272" s="1" t="s">
-        <v>751</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>35</v>
@@ -6927,27 +6927,27 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="B273" s="1" t="s">
+      <c r="C273" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="C273" s="1" t="s">
-        <v>754</v>
-      </c>
       <c r="D273" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B274" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="C274" s="1" t="s">
         <v>755</v>
-      </c>
-      <c r="C274" s="1" t="s">
-        <v>756</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>25</v>
@@ -6955,13 +6955,13 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B275" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="B275" s="1" t="s">
-        <v>762</v>
-      </c>
       <c r="C275" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>47</v>
@@ -6969,13 +6969,13 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B276" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="B276" s="1" t="s">
-        <v>764</v>
-      </c>
       <c r="C276" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>154</v>
@@ -6983,13 +6983,13 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B277" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="B277" s="1" t="s">
+      <c r="C277" s="1" t="s">
         <v>770</v>
-      </c>
-      <c r="C277" s="1" t="s">
-        <v>771</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>47</v>
@@ -6997,16 +6997,16 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
